--- a/健康焦虑数据.xlsx
+++ b/健康焦虑数据.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\57005\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F874F8BB-D9DC-44E1-AA10-7158D42B81DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF80615-9DE3-4BBE-9DE1-563CD6AA132C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{7867C7DF-0CAF-4528-B930-C3ACEC5B4A51}"/>
+    <workbookView xWindow="14780" yWindow="0" windowWidth="10820" windowHeight="15280" xr2:uid="{7867C7DF-0CAF-4528-B930-C3ACEC5B4A51}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -759,7 +759,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -2530,7 +2530,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -3979,7 +3979,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C22">
         <v>2</v>
@@ -4784,7 +4784,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C27">
         <v>2</v>
@@ -4945,7 +4945,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C28">
         <v>2</v>
@@ -5750,7 +5750,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C33">
         <v>2</v>
@@ -8487,7 +8487,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C50">
         <v>2</v>
@@ -8809,7 +8809,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C52">
         <v>2</v>
@@ -11063,7 +11063,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C66">
         <v>2</v>
@@ -12834,7 +12834,7 @@
         <v>76</v>
       </c>
       <c r="B77">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C77">
         <v>2</v>
@@ -13317,7 +13317,7 @@
         <v>79</v>
       </c>
       <c r="B80">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C80">
         <v>2</v>
@@ -13639,7 +13639,7 @@
         <v>81</v>
       </c>
       <c r="B82">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C82">
         <v>2</v>
@@ -14766,7 +14766,7 @@
         <v>88</v>
       </c>
       <c r="B89">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C89">
         <v>2</v>
@@ -14927,7 +14927,7 @@
         <v>89</v>
       </c>
       <c r="B90">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C90">
         <v>2</v>
@@ -15410,7 +15410,7 @@
         <v>92</v>
       </c>
       <c r="B93">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C93">
         <v>1</v>
@@ -15893,7 +15893,7 @@
         <v>95</v>
       </c>
       <c r="B96">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -16376,7 +16376,7 @@
         <v>98</v>
       </c>
       <c r="B99">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -16859,7 +16859,7 @@
         <v>101</v>
       </c>
       <c r="B102">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C102">
         <v>2</v>
@@ -17020,7 +17020,7 @@
         <v>102</v>
       </c>
       <c r="B103">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C103">
         <v>2</v>
